--- a/resources/excel_tables/quest.xlsx
+++ b/resources/excel_tables/quest.xlsx
@@ -4,6 +4,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Quests" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -31,16 +32,16 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
   </numFmts>
   <fonts count="1">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -65,18 +66,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleMedium4" defaultTableStyle="TableStyleMedium9"/>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -456,9 +457,7 @@
       <c r="H2" t="str">
         <v>50</v>
       </c>
-      <c r="I2" t="str">
-        <v/>
-      </c>
+      <c r="I2" t="str"/>
       <c r="J2" t="str">
         <v>与村长对话，了解江湖世界</v>
       </c>
@@ -520,9 +519,7 @@
       <c r="H4" t="str">
         <v>150</v>
       </c>
-      <c r="I4" t="str">
-        <v/>
-      </c>
+      <c r="I4" t="str"/>
       <c r="J4" t="str">
         <v>击败10只竹叶青蛇</v>
       </c>
@@ -552,9 +549,7 @@
       <c r="H5" t="str">
         <v>100</v>
       </c>
-      <c r="I5" t="str">
-        <v/>
-      </c>
+      <c r="I5" t="str"/>
       <c r="J5" t="str">
         <v>收集20个竹笋</v>
       </c>
@@ -616,9 +611,7 @@
       <c r="H7" t="str">
         <v>400</v>
       </c>
-      <c r="I7" t="str">
-        <v/>
-      </c>
+      <c r="I7" t="str"/>
       <c r="J7" t="str">
         <v>探索青竹山的深处</v>
       </c>
@@ -648,9 +641,7 @@
       <c r="H8" t="str">
         <v>600</v>
       </c>
-      <c r="I8" t="str">
-        <v/>
-      </c>
+      <c r="I8" t="str"/>
       <c r="J8" t="str">
         <v>击败东海之滨的精英怪物</v>
       </c>
@@ -680,9 +671,7 @@
       <c r="H9" t="str">
         <v>800</v>
       </c>
-      <c r="I9" t="str">
-        <v/>
-      </c>
+      <c r="I9" t="str"/>
       <c r="J9" t="str">
         <v>首次进入剑华城</v>
       </c>
@@ -744,9 +733,7 @@
       <c r="H11" t="str">
         <v>50</v>
       </c>
-      <c r="I11" t="str">
-        <v/>
-      </c>
+      <c r="I11" t="str"/>
       <c r="J11" t="str">
         <v>击败20只怪物</v>
       </c>
@@ -776,9 +763,7 @@
       <c r="H12" t="str">
         <v>40</v>
       </c>
-      <c r="I12" t="str">
-        <v/>
-      </c>
+      <c r="I12" t="str"/>
       <c r="J12" t="str">
         <v>采集10个资源</v>
       </c>
@@ -808,9 +793,7 @@
       <c r="H13" t="str">
         <v>300</v>
       </c>
-      <c r="I13" t="str">
-        <v/>
-      </c>
+      <c r="I13" t="str"/>
       <c r="J13" t="str">
         <v>完成一次地下城挑战</v>
       </c>
@@ -872,9 +855,7 @@
       <c r="H15" t="str">
         <v>1000</v>
       </c>
-      <c r="I15" t="str">
-        <v/>
-      </c>
+      <c r="I15" t="str"/>
       <c r="J15" t="str">
         <v>完成5次地下城挑战</v>
       </c>
@@ -1009,7 +990,606 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J19"/>
+    <ignoredError sqref="A1:J19" numberStoredAsText="true"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J19"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>QuestID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Type</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Level</v>
+      </c>
+      <c r="E1" t="str">
+        <v>ClassID</v>
+      </c>
+      <c r="F1" t="str">
+        <v>MapID</v>
+      </c>
+      <c r="G1" t="str">
+        <v>ExpReward</v>
+      </c>
+      <c r="H1" t="str">
+        <v>GoldReward</v>
+      </c>
+      <c r="I1" t="str">
+        <v>ItemRewards</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Description</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>1001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>初入江湖</v>
+      </c>
+      <c r="C2" t="str">
+        <v>main</v>
+      </c>
+      <c r="D2" t="str">
+        <v>1</v>
+      </c>
+      <c r="E2" t="str">
+        <v>0</v>
+      </c>
+      <c r="F2" t="str">
+        <v>0</v>
+      </c>
+      <c r="G2" t="str">
+        <v>100</v>
+      </c>
+      <c r="H2" t="str">
+        <v>50</v>
+      </c>
+      <c r="I2" t="str"/>
+      <c r="J2" t="str">
+        <v>与村长对话，了解江湖世界</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>1002</v>
+      </c>
+      <c r="B3" t="str">
+        <v>武器试炼</v>
+      </c>
+      <c r="C3" t="str">
+        <v>main</v>
+      </c>
+      <c r="D3" t="str">
+        <v>3</v>
+      </c>
+      <c r="E3" t="str">
+        <v>0</v>
+      </c>
+      <c r="F3" t="str">
+        <v>0</v>
+      </c>
+      <c r="G3" t="str">
+        <v>200</v>
+      </c>
+      <c r="H3" t="str">
+        <v>100</v>
+      </c>
+      <c r="I3" t="str">
+        <v>[1001]</v>
+      </c>
+      <c r="J3" t="str">
+        <v>获得新手武器</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>1003</v>
+      </c>
+      <c r="B4" t="str">
+        <v>初次战斗</v>
+      </c>
+      <c r="C4" t="str">
+        <v>main</v>
+      </c>
+      <c r="D4" t="str">
+        <v>5</v>
+      </c>
+      <c r="E4" t="str">
+        <v>0</v>
+      </c>
+      <c r="F4" t="str">
+        <v>0</v>
+      </c>
+      <c r="G4" t="str">
+        <v>300</v>
+      </c>
+      <c r="H4" t="str">
+        <v>150</v>
+      </c>
+      <c r="I4" t="str"/>
+      <c r="J4" t="str">
+        <v>击败10只竹叶青蛇</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>1004</v>
+      </c>
+      <c r="B5" t="str">
+        <v>收集竹笋</v>
+      </c>
+      <c r="C5" t="str">
+        <v>collection</v>
+      </c>
+      <c r="D5" t="str">
+        <v>5</v>
+      </c>
+      <c r="E5" t="str">
+        <v>0</v>
+      </c>
+      <c r="F5" t="str">
+        <v>1002</v>
+      </c>
+      <c r="G5" t="str">
+        <v>250</v>
+      </c>
+      <c r="H5" t="str">
+        <v>100</v>
+      </c>
+      <c r="I5" t="str"/>
+      <c r="J5" t="str">
+        <v>收集20个竹笋</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>1005</v>
+      </c>
+      <c r="B6" t="str">
+        <v>装备升级</v>
+      </c>
+      <c r="C6" t="str">
+        <v>main</v>
+      </c>
+      <c r="D6" t="str">
+        <v>10</v>
+      </c>
+      <c r="E6" t="str">
+        <v>0</v>
+      </c>
+      <c r="F6" t="str">
+        <v>0</v>
+      </c>
+      <c r="G6" t="str">
+        <v>500</v>
+      </c>
+      <c r="H6" t="str">
+        <v>300</v>
+      </c>
+      <c r="I6" t="str">
+        <v>[1002]</v>
+      </c>
+      <c r="J6" t="str">
+        <v>获得精铁装备</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>2001</v>
+      </c>
+      <c r="B7" t="str">
+        <v>探索野外</v>
+      </c>
+      <c r="C7" t="str">
+        <v>main</v>
+      </c>
+      <c r="D7" t="str">
+        <v>15</v>
+      </c>
+      <c r="E7" t="str">
+        <v>0</v>
+      </c>
+      <c r="F7" t="str">
+        <v>1002</v>
+      </c>
+      <c r="G7" t="str">
+        <v>800</v>
+      </c>
+      <c r="H7" t="str">
+        <v>400</v>
+      </c>
+      <c r="I7" t="str"/>
+      <c r="J7" t="str">
+        <v>探索青竹山的深处</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>2002</v>
+      </c>
+      <c r="B8" t="str">
+        <v>击败精英</v>
+      </c>
+      <c r="C8" t="str">
+        <v>main</v>
+      </c>
+      <c r="D8" t="str">
+        <v>20</v>
+      </c>
+      <c r="E8" t="str">
+        <v>0</v>
+      </c>
+      <c r="F8" t="str">
+        <v>1003</v>
+      </c>
+      <c r="G8" t="str">
+        <v>1200</v>
+      </c>
+      <c r="H8" t="str">
+        <v>600</v>
+      </c>
+      <c r="I8" t="str"/>
+      <c r="J8" t="str">
+        <v>击败东海之滨的精英怪物</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>2003</v>
+      </c>
+      <c r="B9" t="str">
+        <v>进入主城</v>
+      </c>
+      <c r="C9" t="str">
+        <v>main</v>
+      </c>
+      <c r="D9" t="str">
+        <v>25</v>
+      </c>
+      <c r="E9" t="str">
+        <v>0</v>
+      </c>
+      <c r="F9" t="str">
+        <v>1005</v>
+      </c>
+      <c r="G9" t="str">
+        <v>1500</v>
+      </c>
+      <c r="H9" t="str">
+        <v>800</v>
+      </c>
+      <c r="I9" t="str"/>
+      <c r="J9" t="str">
+        <v>首次进入剑华城</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>2004</v>
+      </c>
+      <c r="B10" t="str">
+        <v>地下城挑战</v>
+      </c>
+      <c r="C10" t="str">
+        <v>dungeon</v>
+      </c>
+      <c r="D10" t="str">
+        <v>30</v>
+      </c>
+      <c r="E10" t="str">
+        <v>0</v>
+      </c>
+      <c r="F10" t="str">
+        <v>1004</v>
+      </c>
+      <c r="G10" t="str">
+        <v>2000</v>
+      </c>
+      <c r="H10" t="str">
+        <v>1000</v>
+      </c>
+      <c r="I10" t="str">
+        <v>[1003]</v>
+      </c>
+      <c r="J10" t="str">
+        <v>完成东海龙宫挑战</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>3001</v>
+      </c>
+      <c r="B11" t="str">
+        <v>每日战斗</v>
+      </c>
+      <c r="C11" t="str">
+        <v>daily</v>
+      </c>
+      <c r="D11" t="str">
+        <v>1</v>
+      </c>
+      <c r="E11" t="str">
+        <v>0</v>
+      </c>
+      <c r="F11" t="str">
+        <v>0</v>
+      </c>
+      <c r="G11" t="str">
+        <v>100</v>
+      </c>
+      <c r="H11" t="str">
+        <v>50</v>
+      </c>
+      <c r="I11" t="str"/>
+      <c r="J11" t="str">
+        <v>击败20只怪物</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3002</v>
+      </c>
+      <c r="B12" t="str">
+        <v>每日采集</v>
+      </c>
+      <c r="C12" t="str">
+        <v>daily</v>
+      </c>
+      <c r="D12" t="str">
+        <v>1</v>
+      </c>
+      <c r="E12" t="str">
+        <v>0</v>
+      </c>
+      <c r="F12" t="str">
+        <v>0</v>
+      </c>
+      <c r="G12" t="str">
+        <v>80</v>
+      </c>
+      <c r="H12" t="str">
+        <v>40</v>
+      </c>
+      <c r="I12" t="str"/>
+      <c r="J12" t="str">
+        <v>采集10个资源</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>3003</v>
+      </c>
+      <c r="B13" t="str">
+        <v>每日副本</v>
+      </c>
+      <c r="C13" t="str">
+        <v>daily</v>
+      </c>
+      <c r="D13" t="str">
+        <v>20</v>
+      </c>
+      <c r="E13" t="str">
+        <v>0</v>
+      </c>
+      <c r="F13" t="str">
+        <v>0</v>
+      </c>
+      <c r="G13" t="str">
+        <v>500</v>
+      </c>
+      <c r="H13" t="str">
+        <v>300</v>
+      </c>
+      <c r="I13" t="str"/>
+      <c r="J13" t="str">
+        <v>完成一次地下城挑战</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>4001</v>
+      </c>
+      <c r="B14" t="str">
+        <v>周常战斗</v>
+      </c>
+      <c r="C14" t="str">
+        <v>weekly</v>
+      </c>
+      <c r="D14" t="str">
+        <v>1</v>
+      </c>
+      <c r="E14" t="str">
+        <v>0</v>
+      </c>
+      <c r="F14" t="str">
+        <v>0</v>
+      </c>
+      <c r="G14" t="str">
+        <v>1000</v>
+      </c>
+      <c r="H14" t="str">
+        <v>500</v>
+      </c>
+      <c r="I14" t="str">
+        <v>[9003]</v>
+      </c>
+      <c r="J14" t="str">
+        <v>累计击败100只怪物</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>4002</v>
+      </c>
+      <c r="B15" t="str">
+        <v>周常副本</v>
+      </c>
+      <c r="C15" t="str">
+        <v>weekly</v>
+      </c>
+      <c r="D15" t="str">
+        <v>20</v>
+      </c>
+      <c r="E15" t="str">
+        <v>0</v>
+      </c>
+      <c r="F15" t="str">
+        <v>0</v>
+      </c>
+      <c r="G15" t="str">
+        <v>2000</v>
+      </c>
+      <c r="H15" t="str">
+        <v>1000</v>
+      </c>
+      <c r="I15" t="str"/>
+      <c r="J15" t="str">
+        <v>完成5次地下城挑战</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>5001</v>
+      </c>
+      <c r="B16" t="str">
+        <v>战士试炼</v>
+      </c>
+      <c r="C16" t="str">
+        <v>class</v>
+      </c>
+      <c r="D16" t="str">
+        <v>10</v>
+      </c>
+      <c r="E16" t="str">
+        <v>1</v>
+      </c>
+      <c r="F16" t="str">
+        <v>0</v>
+      </c>
+      <c r="G16" t="str">
+        <v>500</v>
+      </c>
+      <c r="H16" t="str">
+        <v>200</v>
+      </c>
+      <c r="I16" t="str">
+        <v>[1002]</v>
+      </c>
+      <c r="J16" t="str">
+        <v>战士专属任务，获得精铁剑</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>5002</v>
+      </c>
+      <c r="B17" t="str">
+        <v>法师试炼</v>
+      </c>
+      <c r="C17" t="str">
+        <v>class</v>
+      </c>
+      <c r="D17" t="str">
+        <v>10</v>
+      </c>
+      <c r="E17" t="str">
+        <v>2</v>
+      </c>
+      <c r="F17" t="str">
+        <v>0</v>
+      </c>
+      <c r="G17" t="str">
+        <v>500</v>
+      </c>
+      <c r="H17" t="str">
+        <v>200</v>
+      </c>
+      <c r="I17" t="str">
+        <v>[2002]</v>
+      </c>
+      <c r="J17" t="str">
+        <v>法师专属任务，获得灵木法杖</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>5003</v>
+      </c>
+      <c r="B18" t="str">
+        <v>弓箭手试炼</v>
+      </c>
+      <c r="C18" t="str">
+        <v>class</v>
+      </c>
+      <c r="D18" t="str">
+        <v>10</v>
+      </c>
+      <c r="E18" t="str">
+        <v>3</v>
+      </c>
+      <c r="F18" t="str">
+        <v>0</v>
+      </c>
+      <c r="G18" t="str">
+        <v>500</v>
+      </c>
+      <c r="H18" t="str">
+        <v>200</v>
+      </c>
+      <c r="I18" t="str">
+        <v>[3002]</v>
+      </c>
+      <c r="J18" t="str">
+        <v>弓箭手专属任务，获得精铁弓</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>5004</v>
+      </c>
+      <c r="B19" t="str">
+        <v>刺客试炼</v>
+      </c>
+      <c r="C19" t="str">
+        <v>class</v>
+      </c>
+      <c r="D19" t="str">
+        <v>10</v>
+      </c>
+      <c r="E19" t="str">
+        <v>4</v>
+      </c>
+      <c r="F19" t="str">
+        <v>0</v>
+      </c>
+      <c r="G19" t="str">
+        <v>500</v>
+      </c>
+      <c r="H19" t="str">
+        <v>200</v>
+      </c>
+      <c r="I19" t="str">
+        <v>[4002]</v>
+      </c>
+      <c r="J19" t="str">
+        <v>刺客专属任务，获得精铁匕首</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError sqref="A1:J19" numberStoredAsText="true"/>
   </ignoredErrors>
 </worksheet>
 </file>